--- a/data_output/segur_psd_fit_python/MPsizeBase_v15_05_2026.xlsx
+++ b/data_output/segur_psd_fit_python/MPsizeBase_v15_05_2026.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:F498"/>
+  <dimension ref="A3:F469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
@@ -500,7 +500,7 @@
         <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
         <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>75</v>
       </c>
       <c r="D6" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>85</v>
       </c>
       <c r="D7" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>105</v>
       </c>
       <c r="D9" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
         <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>135</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>140</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>155</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>160</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -808,7 +808,7 @@
         <v>170</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>175</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -852,7 +852,7 @@
         <v>180</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -918,7 +918,7 @@
         <v>195</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C24" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C25" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C26" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C27" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C28" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C29" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C30" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C31" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D31" t="n">
         <v>4</v>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C32" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C33" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D33" t="n">
         <v>4</v>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C34" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C35" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C36" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C37" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C38" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C39" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C40" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C41" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C42" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C43" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C44" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C45" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D45" t="n">
         <v>2</v>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C46" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C47" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C48" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C49" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C50" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C51" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D51" t="n">
         <v>2</v>
@@ -1550,13 +1550,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C52" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C53" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C54" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C55" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="C56" t="n">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="C57" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C58" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C59" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C60" t="n">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C61" t="n">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C62" t="n">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C63" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C64" t="n">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C65" t="n">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>455</v>
+        <v>490</v>
       </c>
       <c r="C66" t="n">
-        <v>460</v>
+        <v>495</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>460</v>
+        <v>505</v>
       </c>
       <c r="C67" t="n">
-        <v>465</v>
+        <v>510</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>475</v>
+        <v>515</v>
       </c>
       <c r="C68" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="C69" t="n">
-        <v>495</v>
+        <v>575</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="C70" t="n">
-        <v>510</v>
+        <v>580</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>515</v>
+        <v>605</v>
       </c>
       <c r="C71" t="n">
-        <v>520</v>
+        <v>610</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>555</v>
+        <v>695</v>
       </c>
       <c r="C72" t="n">
-        <v>560</v>
+        <v>700</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>570</v>
+        <v>780</v>
       </c>
       <c r="C73" t="n">
-        <v>575</v>
+        <v>785</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>575</v>
+        <v>785</v>
       </c>
       <c r="C74" t="n">
-        <v>580</v>
+        <v>790</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>600</v>
+        <v>830</v>
       </c>
       <c r="C75" t="n">
-        <v>605</v>
+        <v>835</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>605</v>
+        <v>835</v>
       </c>
       <c r="C76" t="n">
-        <v>610</v>
+        <v>840</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>695</v>
+        <v>855</v>
       </c>
       <c r="C77" t="n">
-        <v>700</v>
+        <v>860</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>780</v>
+        <v>940</v>
       </c>
       <c r="C78" t="n">
-        <v>785</v>
+        <v>945</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>785</v>
+        <v>1105</v>
       </c>
       <c r="C79" t="n">
-        <v>790</v>
+        <v>1110</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2162,17 +2162,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>830</v>
+        <v>50</v>
       </c>
       <c r="C80" t="n">
-        <v>835</v>
+        <v>55</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2184,17 +2184,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>835</v>
+        <v>60</v>
       </c>
       <c r="C81" t="n">
-        <v>840</v>
+        <v>65</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -2206,17 +2206,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>855</v>
+        <v>70</v>
       </c>
       <c r="C82" t="n">
-        <v>860</v>
+        <v>75</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2228,17 +2228,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>860</v>
+        <v>80</v>
       </c>
       <c r="C83" t="n">
-        <v>865</v>
+        <v>85</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2250,17 +2250,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>940</v>
+        <v>95</v>
       </c>
       <c r="C84" t="n">
-        <v>945</v>
+        <v>100</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -2272,17 +2272,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1105</v>
+        <v>100</v>
       </c>
       <c r="C85" t="n">
-        <v>1110</v>
+        <v>105</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -2294,17 +2294,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1875</v>
+        <v>115</v>
       </c>
       <c r="C86" t="n">
-        <v>1880</v>
+        <v>120</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -2316,17 +2316,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>W2W_river_all</t>
+          <t>W2W_river_fragment</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2100</v>
+        <v>120</v>
       </c>
       <c r="C87" t="n">
-        <v>2105</v>
+        <v>125</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C88" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="D88" t="n">
-        <v>232</v>
+        <v>23</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="C89" t="n">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="D89" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="C90" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="D90" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="C91" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="D91" t="n">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="D92" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="C93" t="n">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="D93" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="C94" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="D94" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -2496,13 +2496,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C95" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -2518,13 +2518,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="C96" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="D96" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -2540,13 +2540,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C97" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="D97" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="C98" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="D98" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="C99" t="n">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="D99" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C100" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="D100" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -2628,13 +2628,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="C101" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="D101" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="C102" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="C103" t="n">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -2694,13 +2694,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="C104" t="n">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="C105" t="n">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="D105" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="C106" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="C107" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="C108" t="n">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="C109" t="n">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="D109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="C110" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="C111" t="n">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="C112" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -2892,13 +2892,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>230</v>
+        <v>295</v>
       </c>
       <c r="C113" t="n">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="C114" t="n">
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="C115" t="n">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="D115" t="n">
         <v>2</v>
@@ -2958,13 +2958,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="C116" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>260</v>
+        <v>325</v>
       </c>
       <c r="C117" t="n">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="C118" t="n">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>275</v>
+        <v>340</v>
       </c>
       <c r="C119" t="n">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="C120" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="C121" t="n">
-        <v>290</v>
+        <v>355</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="C122" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C123" t="n">
-        <v>305</v>
+        <v>425</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>310</v>
+        <v>455</v>
       </c>
       <c r="C124" t="n">
-        <v>315</v>
+        <v>460</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>315</v>
+        <v>460</v>
       </c>
       <c r="C125" t="n">
-        <v>320</v>
+        <v>465</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>325</v>
+        <v>505</v>
       </c>
       <c r="C126" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -3196,124 +3196,124 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>330</v>
+        <v>75</v>
       </c>
       <c r="C127" t="n">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="C128" t="n">
-        <v>345</v>
+        <v>85</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>345</v>
+        <v>95</v>
       </c>
       <c r="C129" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="C130" t="n">
-        <v>355</v>
+        <v>105</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>375</v>
+        <v>115</v>
       </c>
       <c r="C131" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="C132" t="n">
-        <v>385</v>
+        <v>125</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
@@ -3322,64 +3322,64 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>385</v>
+        <v>125</v>
       </c>
       <c r="C133" t="n">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>420</v>
+        <v>135</v>
       </c>
       <c r="C134" t="n">
-        <v>425</v>
+        <v>140</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>455</v>
+        <v>145</v>
       </c>
       <c r="C135" t="n">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -3388,51 +3388,51 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="C136" t="n">
-        <v>465</v>
+        <v>155</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>W2W_river_fragment</t>
+          <t>W2W_river_fiber</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>505</v>
+        <v>155</v>
       </c>
       <c r="C137" t="n">
-        <v>510</v>
+        <v>160</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="C138" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="D138" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="C139" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="C140" t="n">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="D140" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -3508,13 +3508,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="C141" t="n">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="D141" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -3530,13 +3530,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="C142" t="n">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="D142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3552,13 +3552,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="C143" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -3574,13 +3574,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="C144" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="D144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="C145" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="D145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -3618,13 +3618,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="C146" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="C147" t="n">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="D147" t="n">
         <v>2</v>
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c r="C148" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="C149" t="n">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>170</v>
+        <v>255</v>
       </c>
       <c r="C150" t="n">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="C151" t="n">
-        <v>180</v>
+        <v>265</v>
       </c>
       <c r="D151" t="n">
         <v>3</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="C152" t="n">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="C153" t="n">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="C154" t="n">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -3816,13 +3816,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="C155" t="n">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="C156" t="n">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>220</v>
+        <v>295</v>
       </c>
       <c r="C157" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -3882,13 +3882,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="C158" t="n">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="D158" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="C159" t="n">
-        <v>235</v>
+        <v>315</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>235</v>
+        <v>325</v>
       </c>
       <c r="C160" t="n">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="C161" t="n">
-        <v>245</v>
+        <v>335</v>
       </c>
       <c r="D161" t="n">
         <v>2</v>
@@ -3970,13 +3970,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>245</v>
+        <v>340</v>
       </c>
       <c r="C162" t="n">
-        <v>250</v>
+        <v>345</v>
       </c>
       <c r="D162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>250</v>
+        <v>345</v>
       </c>
       <c r="C163" t="n">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4014,13 +4014,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>255</v>
+        <v>360</v>
       </c>
       <c r="C164" t="n">
-        <v>260</v>
+        <v>365</v>
       </c>
       <c r="D164" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>260</v>
+        <v>365</v>
       </c>
       <c r="C165" t="n">
-        <v>265</v>
+        <v>370</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="C166" t="n">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="D166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4080,13 +4080,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="C167" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="C168" t="n">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>285</v>
+        <v>425</v>
       </c>
       <c r="C169" t="n">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="C170" t="n">
-        <v>295</v>
+        <v>435</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>295</v>
+        <v>435</v>
       </c>
       <c r="C171" t="n">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4190,13 +4190,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="C172" t="n">
-        <v>305</v>
+        <v>445</v>
       </c>
       <c r="D172" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>310</v>
+        <v>445</v>
       </c>
       <c r="C173" t="n">
-        <v>315</v>
+        <v>450</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>315</v>
+        <v>450</v>
       </c>
       <c r="C174" t="n">
-        <v>320</v>
+        <v>455</v>
       </c>
       <c r="D174" t="n">
         <v>1</v>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>325</v>
+        <v>455</v>
       </c>
       <c r="C175" t="n">
-        <v>330</v>
+        <v>460</v>
       </c>
       <c r="D175" t="n">
         <v>1</v>
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>330</v>
+        <v>460</v>
       </c>
       <c r="C176" t="n">
-        <v>335</v>
+        <v>465</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>340</v>
+        <v>475</v>
       </c>
       <c r="C177" t="n">
-        <v>345</v>
+        <v>480</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -4322,13 +4322,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>345</v>
+        <v>490</v>
       </c>
       <c r="C178" t="n">
-        <v>350</v>
+        <v>495</v>
       </c>
       <c r="D178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4344,13 +4344,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>360</v>
+        <v>515</v>
       </c>
       <c r="C179" t="n">
-        <v>365</v>
+        <v>520</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -4366,13 +4366,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>365</v>
+        <v>570</v>
       </c>
       <c r="C180" t="n">
-        <v>370</v>
+        <v>575</v>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>370</v>
+        <v>575</v>
       </c>
       <c r="C181" t="n">
-        <v>375</v>
+        <v>580</v>
       </c>
       <c r="D181" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>375</v>
+        <v>605</v>
       </c>
       <c r="C182" t="n">
-        <v>380</v>
+        <v>610</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>380</v>
+        <v>695</v>
       </c>
       <c r="C183" t="n">
-        <v>385</v>
+        <v>700</v>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>395</v>
+        <v>780</v>
       </c>
       <c r="C184" t="n">
-        <v>400</v>
+        <v>785</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
@@ -4476,10 +4476,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>405</v>
+        <v>785</v>
       </c>
       <c r="C185" t="n">
-        <v>410</v>
+        <v>790</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
@@ -4498,13 +4498,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>425</v>
+        <v>830</v>
       </c>
       <c r="C186" t="n">
-        <v>430</v>
+        <v>835</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>430</v>
+        <v>835</v>
       </c>
       <c r="C187" t="n">
-        <v>435</v>
+        <v>840</v>
       </c>
       <c r="D187" t="n">
         <v>1</v>
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>435</v>
+        <v>855</v>
       </c>
       <c r="C188" t="n">
-        <v>440</v>
+        <v>860</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>440</v>
+        <v>940</v>
       </c>
       <c r="C189" t="n">
-        <v>445</v>
+        <v>945</v>
       </c>
       <c r="D189" t="n">
         <v>1</v>
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>445</v>
+        <v>1105</v>
       </c>
       <c r="C190" t="n">
-        <v>450</v>
+        <v>1110</v>
       </c>
       <c r="D190" t="n">
         <v>1</v>
@@ -4604,485 +4604,485 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>450</v>
+        <v>50</v>
       </c>
       <c r="C191" t="n">
-        <v>455</v>
+        <v>55</v>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>455</v>
+        <v>60</v>
       </c>
       <c r="C192" t="n">
-        <v>460</v>
+        <v>65</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="C193" t="n">
-        <v>465</v>
+        <v>75</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>475</v>
+        <v>80</v>
       </c>
       <c r="C194" t="n">
-        <v>480</v>
+        <v>85</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>490</v>
+        <v>95</v>
       </c>
       <c r="C195" t="n">
-        <v>495</v>
+        <v>100</v>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>515</v>
+        <v>100</v>
       </c>
       <c r="C196" t="n">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>555</v>
+        <v>115</v>
       </c>
       <c r="C197" t="n">
-        <v>560</v>
+        <v>120</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>570</v>
+        <v>120</v>
       </c>
       <c r="C198" t="n">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="C199" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="C200" t="n">
-        <v>605</v>
+        <v>135</v>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>605</v>
+        <v>135</v>
       </c>
       <c r="C201" t="n">
-        <v>610</v>
+        <v>140</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>695</v>
+        <v>145</v>
       </c>
       <c r="C202" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>780</v>
+        <v>150</v>
       </c>
       <c r="C203" t="n">
-        <v>785</v>
+        <v>155</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>785</v>
+        <v>155</v>
       </c>
       <c r="C204" t="n">
-        <v>790</v>
+        <v>160</v>
       </c>
       <c r="D204" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>830</v>
+        <v>165</v>
       </c>
       <c r="C205" t="n">
-        <v>835</v>
+        <v>170</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>835</v>
+        <v>170</v>
       </c>
       <c r="C206" t="n">
-        <v>840</v>
+        <v>175</v>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>855</v>
+        <v>175</v>
       </c>
       <c r="C207" t="n">
-        <v>860</v>
+        <v>180</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>860</v>
+        <v>180</v>
       </c>
       <c r="C208" t="n">
-        <v>865</v>
+        <v>185</v>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>940</v>
+        <v>185</v>
       </c>
       <c r="C209" t="n">
-        <v>945</v>
+        <v>190</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1105</v>
+        <v>190</v>
       </c>
       <c r="C210" t="n">
-        <v>1110</v>
+        <v>195</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1875</v>
+        <v>200</v>
       </c>
       <c r="C211" t="n">
-        <v>1880</v>
+        <v>205</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>W2W_river_fiber</t>
+          <t>W2W_sediment_all</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>2100</v>
+        <v>205</v>
       </c>
       <c r="C212" t="n">
-        <v>2105</v>
+        <v>210</v>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>50</v>
+        <v>215</v>
       </c>
       <c r="C213" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="D213" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="C214" t="n">
-        <v>65</v>
+        <v>225</v>
       </c>
       <c r="D214" t="n">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>70</v>
+        <v>225</v>
       </c>
       <c r="C215" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="D215" t="n">
         <v>10</v>
@@ -5158,13 +5158,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="C216" t="n">
-        <v>85</v>
+        <v>235</v>
       </c>
       <c r="D216" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="C217" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="D217" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -5202,13 +5202,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="C218" t="n">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="D218" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="C219" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D219" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="C220" t="n">
-        <v>125</v>
+        <v>255</v>
       </c>
       <c r="D220" t="n">
         <v>2</v>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>125</v>
+        <v>255</v>
       </c>
       <c r="C221" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="D221" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E221" t="n">
         <v>0</v>
@@ -5290,13 +5290,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="C222" t="n">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="D222" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E222" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="C223" t="n">
-        <v>140</v>
+        <v>275</v>
       </c>
       <c r="D223" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
@@ -5334,13 +5334,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="C224" t="n">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="D224" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E224" t="n">
         <v>0</v>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="C225" t="n">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="D225" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E225" t="n">
         <v>0</v>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="C226" t="n">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="D226" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="C227" t="n">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="D227" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E227" t="n">
         <v>0</v>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="C228" t="n">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="D228" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E228" t="n">
         <v>0</v>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="C229" t="n">
-        <v>180</v>
+        <v>305</v>
       </c>
       <c r="D229" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E229" t="n">
         <v>0</v>
@@ -5466,13 +5466,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>180</v>
+        <v>305</v>
       </c>
       <c r="C230" t="n">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="D230" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E230" t="n">
         <v>0</v>
@@ -5488,13 +5488,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>185</v>
+        <v>310</v>
       </c>
       <c r="C231" t="n">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="D231" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E231" t="n">
         <v>0</v>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="C232" t="n">
-        <v>195</v>
+        <v>320</v>
       </c>
       <c r="D232" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E232" t="n">
         <v>0</v>
@@ -5532,13 +5532,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="C233" t="n">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="D233" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E233" t="n">
         <v>0</v>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="C234" t="n">
-        <v>210</v>
+        <v>335</v>
       </c>
       <c r="D234" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E234" t="n">
         <v>0</v>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="C235" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="D235" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E235" t="n">
         <v>0</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="C236" t="n">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="D236" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E236" t="n">
         <v>0</v>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="C237" t="n">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="D237" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E237" t="n">
         <v>0</v>
@@ -5642,13 +5642,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="C238" t="n">
-        <v>235</v>
+        <v>360</v>
       </c>
       <c r="D238" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
         <v>0</v>
@@ -5664,13 +5664,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>235</v>
+        <v>365</v>
       </c>
       <c r="C239" t="n">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="D239" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
@@ -5686,13 +5686,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="C240" t="n">
-        <v>245</v>
+        <v>375</v>
       </c>
       <c r="D240" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E240" t="n">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>245</v>
+        <v>375</v>
       </c>
       <c r="C241" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="D241" t="n">
         <v>2</v>
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="C242" t="n">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E242" t="n">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="C243" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="D243" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E243" t="n">
         <v>0</v>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="C244" t="n">
-        <v>265</v>
+        <v>395</v>
       </c>
       <c r="D244" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E244" t="n">
         <v>0</v>
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="C245" t="n">
-        <v>275</v>
+        <v>400</v>
       </c>
       <c r="D245" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E245" t="n">
         <v>0</v>
@@ -5818,13 +5818,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>275</v>
+        <v>400</v>
       </c>
       <c r="C246" t="n">
-        <v>280</v>
+        <v>405</v>
       </c>
       <c r="D246" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E246" t="n">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>280</v>
+        <v>405</v>
       </c>
       <c r="C247" t="n">
-        <v>285</v>
+        <v>410</v>
       </c>
       <c r="D247" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E247" t="n">
         <v>0</v>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>285</v>
+        <v>410</v>
       </c>
       <c r="C248" t="n">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="D248" t="n">
         <v>2</v>
@@ -5884,13 +5884,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="C249" t="n">
-        <v>295</v>
+        <v>420</v>
       </c>
       <c r="D249" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E249" t="n">
         <v>0</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>295</v>
+        <v>425</v>
       </c>
       <c r="C250" t="n">
-        <v>300</v>
+        <v>430</v>
       </c>
       <c r="D250" t="n">
         <v>3</v>
@@ -5928,13 +5928,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>300</v>
+        <v>435</v>
       </c>
       <c r="C251" t="n">
-        <v>305</v>
+        <v>440</v>
       </c>
       <c r="D251" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E251" t="n">
         <v>0</v>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>305</v>
+        <v>455</v>
       </c>
       <c r="C252" t="n">
-        <v>310</v>
+        <v>460</v>
       </c>
       <c r="D252" t="n">
         <v>1</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>310</v>
+        <v>460</v>
       </c>
       <c r="C253" t="n">
-        <v>315</v>
+        <v>465</v>
       </c>
       <c r="D253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E253" t="n">
         <v>0</v>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>315</v>
+        <v>470</v>
       </c>
       <c r="C254" t="n">
-        <v>320</v>
+        <v>475</v>
       </c>
       <c r="D254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E254" t="n">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>325</v>
+        <v>480</v>
       </c>
       <c r="C255" t="n">
-        <v>330</v>
+        <v>485</v>
       </c>
       <c r="D255" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E255" t="n">
         <v>0</v>
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>330</v>
+        <v>485</v>
       </c>
       <c r="C256" t="n">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="C257" t="n">
-        <v>340</v>
+        <v>495</v>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257" t="n">
         <v>0</v>
@@ -6082,13 +6082,13 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>345</v>
+        <v>510</v>
       </c>
       <c r="C258" t="n">
-        <v>350</v>
+        <v>515</v>
       </c>
       <c r="D258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258" t="n">
         <v>0</v>
@@ -6104,13 +6104,13 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>350</v>
+        <v>515</v>
       </c>
       <c r="C259" t="n">
-        <v>355</v>
+        <v>520</v>
       </c>
       <c r="D259" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>355</v>
+        <v>520</v>
       </c>
       <c r="C260" t="n">
-        <v>360</v>
+        <v>525</v>
       </c>
       <c r="D260" t="n">
         <v>1</v>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>365</v>
+        <v>535</v>
       </c>
       <c r="C261" t="n">
-        <v>370</v>
+        <v>540</v>
       </c>
       <c r="D261" t="n">
         <v>1</v>
@@ -6170,13 +6170,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>370</v>
+        <v>540</v>
       </c>
       <c r="C262" t="n">
-        <v>375</v>
+        <v>545</v>
       </c>
       <c r="D262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262" t="n">
         <v>0</v>
@@ -6192,13 +6192,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>375</v>
+        <v>555</v>
       </c>
       <c r="C263" t="n">
-        <v>380</v>
+        <v>560</v>
       </c>
       <c r="D263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E263" t="n">
         <v>0</v>
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>380</v>
+        <v>560</v>
       </c>
       <c r="C264" t="n">
-        <v>385</v>
+        <v>565</v>
       </c>
       <c r="D264" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E264" t="n">
         <v>0</v>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>385</v>
+        <v>570</v>
       </c>
       <c r="C265" t="n">
-        <v>390</v>
+        <v>575</v>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E265" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="C266" t="n">
-        <v>395</v>
+        <v>585</v>
       </c>
       <c r="D266" t="n">
         <v>1</v>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>395</v>
+        <v>585</v>
       </c>
       <c r="C267" t="n">
-        <v>400</v>
+        <v>590</v>
       </c>
       <c r="D267" t="n">
         <v>1</v>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C268" t="n">
-        <v>405</v>
+        <v>605</v>
       </c>
       <c r="D268" t="n">
         <v>1</v>
@@ -6324,13 +6324,13 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>405</v>
+        <v>625</v>
       </c>
       <c r="C269" t="n">
-        <v>410</v>
+        <v>630</v>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E269" t="n">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>410</v>
+        <v>645</v>
       </c>
       <c r="C270" t="n">
-        <v>415</v>
+        <v>650</v>
       </c>
       <c r="D270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
         <v>0</v>
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>415</v>
+        <v>655</v>
       </c>
       <c r="C271" t="n">
-        <v>420</v>
+        <v>660</v>
       </c>
       <c r="D271" t="n">
         <v>1</v>
@@ -6390,13 +6390,13 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>425</v>
+        <v>695</v>
       </c>
       <c r="C272" t="n">
-        <v>430</v>
+        <v>700</v>
       </c>
       <c r="D272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
@@ -6412,13 +6412,13 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>435</v>
+        <v>835</v>
       </c>
       <c r="C273" t="n">
-        <v>440</v>
+        <v>840</v>
       </c>
       <c r="D273" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>455</v>
+        <v>880</v>
       </c>
       <c r="C274" t="n">
-        <v>460</v>
+        <v>885</v>
       </c>
       <c r="D274" t="n">
         <v>1</v>
@@ -6456,13 +6456,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>460</v>
+        <v>930</v>
       </c>
       <c r="C275" t="n">
-        <v>465</v>
+        <v>935</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>470</v>
+        <v>950</v>
       </c>
       <c r="C276" t="n">
-        <v>475</v>
+        <v>955</v>
       </c>
       <c r="D276" t="n">
         <v>1</v>
@@ -6500,13 +6500,13 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>480</v>
+        <v>1050</v>
       </c>
       <c r="C277" t="n">
-        <v>485</v>
+        <v>1055</v>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
@@ -6522,10 +6522,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>485</v>
+        <v>1115</v>
       </c>
       <c r="C278" t="n">
-        <v>490</v>
+        <v>1120</v>
       </c>
       <c r="D278" t="n">
         <v>1</v>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>490</v>
+        <v>1150</v>
       </c>
       <c r="C279" t="n">
-        <v>495</v>
+        <v>1155</v>
       </c>
       <c r="D279" t="n">
         <v>1</v>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>510</v>
+        <v>1285</v>
       </c>
       <c r="C280" t="n">
-        <v>515</v>
+        <v>1290</v>
       </c>
       <c r="D280" t="n">
         <v>1</v>
@@ -6584,17 +6584,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>515</v>
+        <v>50</v>
       </c>
       <c r="C281" t="n">
-        <v>520</v>
+        <v>55</v>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
@@ -6606,17 +6606,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>520</v>
+        <v>60</v>
       </c>
       <c r="C282" t="n">
-        <v>525</v>
+        <v>65</v>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E282" t="n">
         <v>0</v>
@@ -6628,17 +6628,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>525</v>
+        <v>70</v>
       </c>
       <c r="C283" t="n">
-        <v>530</v>
+        <v>75</v>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E283" t="n">
         <v>0</v>
@@ -6650,17 +6650,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>535</v>
+        <v>80</v>
       </c>
       <c r="C284" t="n">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="E284" t="n">
         <v>0</v>
@@ -6672,17 +6672,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>540</v>
+        <v>95</v>
       </c>
       <c r="C285" t="n">
-        <v>545</v>
+        <v>100</v>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E285" t="n">
         <v>0</v>
@@ -6694,17 +6694,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>555</v>
+        <v>100</v>
       </c>
       <c r="C286" t="n">
-        <v>560</v>
+        <v>105</v>
       </c>
       <c r="D286" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="E286" t="n">
         <v>0</v>
@@ -6716,17 +6716,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>560</v>
+        <v>115</v>
       </c>
       <c r="C287" t="n">
-        <v>565</v>
+        <v>120</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>570</v>
+        <v>120</v>
       </c>
       <c r="C288" t="n">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="D288" t="n">
         <v>2</v>
@@ -6760,17 +6760,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="C289" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E289" t="n">
         <v>0</v>
@@ -6782,17 +6782,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="C290" t="n">
-        <v>585</v>
+        <v>135</v>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E290" t="n">
         <v>0</v>
@@ -6804,17 +6804,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>585</v>
+        <v>135</v>
       </c>
       <c r="C291" t="n">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E291" t="n">
         <v>0</v>
@@ -6826,17 +6826,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>600</v>
+        <v>145</v>
       </c>
       <c r="C292" t="n">
-        <v>605</v>
+        <v>150</v>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E292" t="n">
         <v>0</v>
@@ -6848,17 +6848,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>625</v>
+        <v>150</v>
       </c>
       <c r="C293" t="n">
-        <v>630</v>
+        <v>155</v>
       </c>
       <c r="D293" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E293" t="n">
         <v>0</v>
@@ -6870,17 +6870,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>645</v>
+        <v>155</v>
       </c>
       <c r="C294" t="n">
-        <v>650</v>
+        <v>160</v>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E294" t="n">
         <v>0</v>
@@ -6892,17 +6892,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>655</v>
+        <v>165</v>
       </c>
       <c r="C295" t="n">
-        <v>660</v>
+        <v>170</v>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E295" t="n">
         <v>0</v>
@@ -6914,17 +6914,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>695</v>
+        <v>170</v>
       </c>
       <c r="C296" t="n">
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E296" t="n">
         <v>0</v>
@@ -6936,17 +6936,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>835</v>
+        <v>175</v>
       </c>
       <c r="C297" t="n">
-        <v>840</v>
+        <v>180</v>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E297" t="n">
         <v>0</v>
@@ -6958,17 +6958,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>880</v>
+        <v>180</v>
       </c>
       <c r="C298" t="n">
-        <v>885</v>
+        <v>185</v>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E298" t="n">
         <v>0</v>
@@ -6980,17 +6980,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>930</v>
+        <v>185</v>
       </c>
       <c r="C299" t="n">
-        <v>935</v>
+        <v>190</v>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E299" t="n">
         <v>0</v>
@@ -7002,17 +7002,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>950</v>
+        <v>190</v>
       </c>
       <c r="C300" t="n">
-        <v>955</v>
+        <v>195</v>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E300" t="n">
         <v>0</v>
@@ -7024,17 +7024,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="C301" t="n">
-        <v>1055</v>
+        <v>205</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E301" t="n">
         <v>0</v>
@@ -7046,17 +7046,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>1115</v>
+        <v>205</v>
       </c>
       <c r="C302" t="n">
-        <v>1120</v>
+        <v>210</v>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E302" t="n">
         <v>0</v>
@@ -7068,17 +7068,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1150</v>
+        <v>215</v>
       </c>
       <c r="C303" t="n">
-        <v>1155</v>
+        <v>220</v>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E303" t="n">
         <v>0</v>
@@ -7090,17 +7090,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>W2W_sediment_all</t>
+          <t>W2W_sediment_fragment</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>1285</v>
+        <v>220</v>
       </c>
       <c r="C304" t="n">
-        <v>1290</v>
+        <v>225</v>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E304" t="n">
         <v>0</v>
@@ -7116,13 +7116,13 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="C305" t="n">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="D305" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="E305" t="n">
         <v>0</v>
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="C306" t="n">
-        <v>65</v>
+        <v>235</v>
       </c>
       <c r="D306" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="E306" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C307" t="n">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="D307" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E307" t="n">
         <v>0</v>
@@ -7182,13 +7182,13 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="C308" t="n">
-        <v>85</v>
+        <v>245</v>
       </c>
       <c r="D308" t="n">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="E308" t="n">
         <v>0</v>
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>95</v>
+        <v>255</v>
       </c>
       <c r="C309" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="D309" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E309" t="n">
         <v>0</v>
@@ -7226,13 +7226,13 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="C310" t="n">
-        <v>105</v>
+        <v>265</v>
       </c>
       <c r="D310" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="E310" t="n">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>115</v>
+        <v>270</v>
       </c>
       <c r="C311" t="n">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="D311" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="E311" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="C312" t="n">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="D312" t="n">
         <v>2</v>
@@ -7292,13 +7292,13 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="C313" t="n">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="D313" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E313" t="n">
         <v>0</v>
@@ -7314,13 +7314,13 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="C314" t="n">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="D314" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
@@ -7336,13 +7336,13 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="C315" t="n">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="D315" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="E315" t="n">
         <v>0</v>
@@ -7358,13 +7358,13 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="C316" t="n">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="D316" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E316" t="n">
         <v>0</v>
@@ -7380,13 +7380,13 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="C317" t="n">
-        <v>155</v>
+        <v>315</v>
       </c>
       <c r="D317" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E317" t="n">
         <v>0</v>
@@ -7402,13 +7402,13 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>155</v>
+        <v>325</v>
       </c>
       <c r="C318" t="n">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="D318" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="C319" t="n">
-        <v>170</v>
+        <v>335</v>
       </c>
       <c r="D319" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E319" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>170</v>
+        <v>335</v>
       </c>
       <c r="C320" t="n">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="D320" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E320" t="n">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>175</v>
+        <v>345</v>
       </c>
       <c r="C321" t="n">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="D321" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E321" t="n">
         <v>0</v>
@@ -7490,13 +7490,13 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="C322" t="n">
-        <v>185</v>
+        <v>355</v>
       </c>
       <c r="D322" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E322" t="n">
         <v>0</v>
@@ -7512,13 +7512,13 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>185</v>
+        <v>365</v>
       </c>
       <c r="C323" t="n">
-        <v>190</v>
+        <v>370</v>
       </c>
       <c r="D323" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E323" t="n">
         <v>0</v>
@@ -7534,13 +7534,13 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>190</v>
+        <v>370</v>
       </c>
       <c r="C324" t="n">
-        <v>195</v>
+        <v>375</v>
       </c>
       <c r="D324" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E324" t="n">
         <v>0</v>
@@ -7556,13 +7556,13 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>200</v>
+        <v>375</v>
       </c>
       <c r="C325" t="n">
-        <v>205</v>
+        <v>380</v>
       </c>
       <c r="D325" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E325" t="n">
         <v>0</v>
@@ -7578,13 +7578,13 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>205</v>
+        <v>385</v>
       </c>
       <c r="C326" t="n">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="D326" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E326" t="n">
         <v>0</v>
@@ -7600,13 +7600,13 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>215</v>
+        <v>390</v>
       </c>
       <c r="C327" t="n">
-        <v>220</v>
+        <v>395</v>
       </c>
       <c r="D327" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E327" t="n">
         <v>0</v>
@@ -7622,13 +7622,13 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>220</v>
+        <v>405</v>
       </c>
       <c r="C328" t="n">
-        <v>225</v>
+        <v>410</v>
       </c>
       <c r="D328" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E328" t="n">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>225</v>
+        <v>410</v>
       </c>
       <c r="C329" t="n">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="D329" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E329" t="n">
         <v>0</v>
@@ -7666,13 +7666,13 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>230</v>
+        <v>425</v>
       </c>
       <c r="C330" t="n">
-        <v>235</v>
+        <v>430</v>
       </c>
       <c r="D330" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E330" t="n">
         <v>0</v>
@@ -7688,13 +7688,13 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>235</v>
+        <v>435</v>
       </c>
       <c r="C331" t="n">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="D331" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E331" t="n">
         <v>0</v>
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>240</v>
+        <v>455</v>
       </c>
       <c r="C332" t="n">
-        <v>245</v>
+        <v>460</v>
       </c>
       <c r="D332" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E332" t="n">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>255</v>
+        <v>485</v>
       </c>
       <c r="C333" t="n">
-        <v>260</v>
+        <v>490</v>
       </c>
       <c r="D333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E333" t="n">
         <v>0</v>
@@ -7754,13 +7754,13 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="C334" t="n">
-        <v>265</v>
+        <v>525</v>
       </c>
       <c r="D334" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E334" t="n">
         <v>0</v>
@@ -7776,13 +7776,13 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>270</v>
+        <v>535</v>
       </c>
       <c r="C335" t="n">
-        <v>275</v>
+        <v>540</v>
       </c>
       <c r="D335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E335" t="n">
         <v>0</v>
@@ -7798,13 +7798,13 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>275</v>
+        <v>555</v>
       </c>
       <c r="C336" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="D336" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E336" t="n">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>280</v>
+        <v>645</v>
       </c>
       <c r="C337" t="n">
-        <v>285</v>
+        <v>650</v>
       </c>
       <c r="D337" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E337" t="n">
         <v>0</v>
@@ -7838,14 +7838,14 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="C338" t="n">
-        <v>290</v>
+        <v>85</v>
       </c>
       <c r="D338" t="n">
         <v>1</v>
@@ -7854,42 +7854,42 @@
         <v>0</v>
       </c>
       <c r="F338" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="C339" t="n">
-        <v>295</v>
+        <v>105</v>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E339" t="n">
         <v>0</v>
       </c>
       <c r="F339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>295</v>
+        <v>115</v>
       </c>
       <c r="C340" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="D340" t="n">
         <v>2</v>
@@ -7898,64 +7898,64 @@
         <v>0</v>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="C341" t="n">
-        <v>305</v>
+        <v>130</v>
       </c>
       <c r="D341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E341" t="n">
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="C342" t="n">
-        <v>315</v>
+        <v>140</v>
       </c>
       <c r="D342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E342" t="n">
         <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>325</v>
+        <v>145</v>
       </c>
       <c r="C343" t="n">
-        <v>330</v>
+        <v>150</v>
       </c>
       <c r="D343" t="n">
         <v>1</v>
@@ -7964,86 +7964,86 @@
         <v>0</v>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>330</v>
+        <v>150</v>
       </c>
       <c r="C344" t="n">
-        <v>335</v>
+        <v>155</v>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E344" t="n">
         <v>0</v>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>335</v>
+        <v>155</v>
       </c>
       <c r="C345" t="n">
-        <v>340</v>
+        <v>160</v>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E345" t="n">
         <v>0</v>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>345</v>
+        <v>170</v>
       </c>
       <c r="C346" t="n">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="D346" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E346" t="n">
         <v>0</v>
       </c>
       <c r="F346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="C347" t="n">
-        <v>355</v>
+        <v>180</v>
       </c>
       <c r="D347" t="n">
         <v>1</v>
@@ -8052,152 +8052,152 @@
         <v>0</v>
       </c>
       <c r="F347" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>365</v>
+        <v>180</v>
       </c>
       <c r="C348" t="n">
-        <v>370</v>
+        <v>185</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E348" t="n">
         <v>0</v>
       </c>
       <c r="F348" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>370</v>
+        <v>185</v>
       </c>
       <c r="C349" t="n">
-        <v>375</v>
+        <v>190</v>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E349" t="n">
         <v>0</v>
       </c>
       <c r="F349" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="C350" t="n">
-        <v>380</v>
+        <v>205</v>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E350" t="n">
         <v>0</v>
       </c>
       <c r="F350" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>385</v>
+        <v>205</v>
       </c>
       <c r="C351" t="n">
-        <v>390</v>
+        <v>210</v>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E351" t="n">
         <v>0</v>
       </c>
       <c r="F351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>390</v>
+        <v>215</v>
       </c>
       <c r="C352" t="n">
-        <v>395</v>
+        <v>220</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E352" t="n">
         <v>0</v>
       </c>
       <c r="F352" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>405</v>
+        <v>220</v>
       </c>
       <c r="C353" t="n">
-        <v>410</v>
+        <v>225</v>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E353" t="n">
         <v>0</v>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>410</v>
+        <v>225</v>
       </c>
       <c r="C354" t="n">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="D354" t="n">
         <v>2</v>
@@ -8206,42 +8206,42 @@
         <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>425</v>
+        <v>230</v>
       </c>
       <c r="C355" t="n">
-        <v>430</v>
+        <v>235</v>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E355" t="n">
         <v>0</v>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="C356" t="n">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="D356" t="n">
         <v>1</v>
@@ -8250,20 +8250,20 @@
         <v>0</v>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>455</v>
+        <v>240</v>
       </c>
       <c r="C357" t="n">
-        <v>460</v>
+        <v>245</v>
       </c>
       <c r="D357" t="n">
         <v>1</v>
@@ -8272,130 +8272,130 @@
         <v>0</v>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>485</v>
+        <v>245</v>
       </c>
       <c r="C358" t="n">
-        <v>490</v>
+        <v>250</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E358" t="n">
         <v>0</v>
       </c>
       <c r="F358" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>520</v>
+        <v>250</v>
       </c>
       <c r="C359" t="n">
-        <v>525</v>
+        <v>255</v>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E359" t="n">
         <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>535</v>
+        <v>255</v>
       </c>
       <c r="C360" t="n">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E360" t="n">
         <v>0</v>
       </c>
       <c r="F360" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>555</v>
+        <v>260</v>
       </c>
       <c r="C361" t="n">
-        <v>560</v>
+        <v>265</v>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E361" t="n">
         <v>0</v>
       </c>
       <c r="F361" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>575</v>
+        <v>270</v>
       </c>
       <c r="C362" t="n">
-        <v>580</v>
+        <v>275</v>
       </c>
       <c r="D362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E362" t="n">
         <v>0</v>
       </c>
       <c r="F362" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>W2W_sediment_fragment</t>
+          <t>W2W_sediment_fiber</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>645</v>
+        <v>275</v>
       </c>
       <c r="C363" t="n">
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="D363" t="n">
         <v>1</v>
@@ -8404,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -8414,10 +8414,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="C364" t="n">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="D364" t="n">
         <v>1</v>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>100</v>
+        <v>285</v>
       </c>
       <c r="C365" t="n">
-        <v>105</v>
+        <v>290</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>115</v>
+        <v>290</v>
       </c>
       <c r="C366" t="n">
-        <v>120</v>
+        <v>295</v>
       </c>
       <c r="D366" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E366" t="n">
         <v>0</v>
@@ -8480,10 +8480,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>125</v>
+        <v>295</v>
       </c>
       <c r="C367" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="D367" t="n">
         <v>1</v>
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="C368" t="n">
-        <v>140</v>
+        <v>305</v>
       </c>
       <c r="D368" t="n">
         <v>2</v>
@@ -8524,13 +8524,13 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>145</v>
+        <v>305</v>
       </c>
       <c r="C369" t="n">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E369" t="n">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>150</v>
+        <v>315</v>
       </c>
       <c r="C370" t="n">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E370" t="n">
         <v>0</v>
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>155</v>
+        <v>325</v>
       </c>
       <c r="C371" t="n">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E371" t="n">
         <v>0</v>
@@ -8590,13 +8590,13 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>170</v>
+        <v>335</v>
       </c>
       <c r="C372" t="n">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="D372" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E372" t="n">
         <v>0</v>
@@ -8612,13 +8612,13 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="C373" t="n">
-        <v>180</v>
+        <v>355</v>
       </c>
       <c r="D373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E373" t="n">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>180</v>
+        <v>355</v>
       </c>
       <c r="C374" t="n">
-        <v>185</v>
+        <v>360</v>
       </c>
       <c r="D374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E374" t="n">
         <v>0</v>
@@ -8656,13 +8656,13 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="C375" t="n">
-        <v>190</v>
+        <v>375</v>
       </c>
       <c r="D375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E375" t="n">
         <v>0</v>
@@ -8678,13 +8678,13 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="C376" t="n">
-        <v>205</v>
+        <v>385</v>
       </c>
       <c r="D376" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E376" t="n">
         <v>0</v>
@@ -8700,13 +8700,13 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>205</v>
+        <v>395</v>
       </c>
       <c r="C377" t="n">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="D377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E377" t="n">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>215</v>
+        <v>400</v>
       </c>
       <c r="C378" t="n">
-        <v>220</v>
+        <v>405</v>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E378" t="n">
         <v>0</v>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>220</v>
+        <v>415</v>
       </c>
       <c r="C379" t="n">
-        <v>225</v>
+        <v>420</v>
       </c>
       <c r="D379" t="n">
         <v>1</v>
@@ -8766,13 +8766,13 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="C380" t="n">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="D380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E380" t="n">
         <v>0</v>
@@ -8788,13 +8788,13 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>230</v>
+        <v>435</v>
       </c>
       <c r="C381" t="n">
-        <v>235</v>
+        <v>440</v>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E381" t="n">
         <v>0</v>
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>235</v>
+        <v>460</v>
       </c>
       <c r="C382" t="n">
-        <v>240</v>
+        <v>465</v>
       </c>
       <c r="D382" t="n">
         <v>1</v>
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="C383" t="n">
-        <v>245</v>
+        <v>475</v>
       </c>
       <c r="D383" t="n">
         <v>1</v>
@@ -8854,10 +8854,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>245</v>
+        <v>480</v>
       </c>
       <c r="C384" t="n">
-        <v>250</v>
+        <v>485</v>
       </c>
       <c r="D384" t="n">
         <v>2</v>
@@ -8876,13 +8876,13 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>250</v>
+        <v>490</v>
       </c>
       <c r="C385" t="n">
-        <v>255</v>
+        <v>495</v>
       </c>
       <c r="D385" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E385" t="n">
         <v>0</v>
@@ -8898,13 +8898,13 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="C386" t="n">
-        <v>260</v>
+        <v>515</v>
       </c>
       <c r="D386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E386" t="n">
         <v>0</v>
@@ -8920,13 +8920,13 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>260</v>
+        <v>515</v>
       </c>
       <c r="C387" t="n">
-        <v>265</v>
+        <v>520</v>
       </c>
       <c r="D387" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E387" t="n">
         <v>0</v>
@@ -8942,13 +8942,13 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>270</v>
+        <v>540</v>
       </c>
       <c r="C388" t="n">
-        <v>275</v>
+        <v>545</v>
       </c>
       <c r="D388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E388" t="n">
         <v>0</v>
@@ -8964,13 +8964,13 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>275</v>
+        <v>555</v>
       </c>
       <c r="C389" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E389" t="n">
         <v>0</v>
@@ -8986,10 +8986,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="C390" t="n">
-        <v>285</v>
+        <v>565</v>
       </c>
       <c r="D390" t="n">
         <v>1</v>
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>285</v>
+        <v>570</v>
       </c>
       <c r="C391" t="n">
-        <v>290</v>
+        <v>575</v>
       </c>
       <c r="D391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E391" t="n">
         <v>0</v>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>290</v>
+        <v>580</v>
       </c>
       <c r="C392" t="n">
-        <v>295</v>
+        <v>585</v>
       </c>
       <c r="D392" t="n">
         <v>1</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>295</v>
+        <v>585</v>
       </c>
       <c r="C393" t="n">
-        <v>300</v>
+        <v>590</v>
       </c>
       <c r="D393" t="n">
         <v>1</v>
@@ -9074,13 +9074,13 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="C394" t="n">
-        <v>305</v>
+        <v>605</v>
       </c>
       <c r="D394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E394" t="n">
         <v>0</v>
@@ -9096,13 +9096,13 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>305</v>
+        <v>625</v>
       </c>
       <c r="C395" t="n">
-        <v>310</v>
+        <v>630</v>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E395" t="n">
         <v>0</v>
@@ -9118,13 +9118,13 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>315</v>
+        <v>655</v>
       </c>
       <c r="C396" t="n">
-        <v>320</v>
+        <v>660</v>
       </c>
       <c r="D396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E396" t="n">
         <v>0</v>
@@ -9140,13 +9140,13 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>325</v>
+        <v>695</v>
       </c>
       <c r="C397" t="n">
-        <v>330</v>
+        <v>700</v>
       </c>
       <c r="D397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E397" t="n">
         <v>0</v>
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>335</v>
+        <v>835</v>
       </c>
       <c r="C398" t="n">
-        <v>340</v>
+        <v>840</v>
       </c>
       <c r="D398" t="n">
         <v>1</v>
@@ -9184,13 +9184,13 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="C399" t="n">
-        <v>355</v>
+        <v>885</v>
       </c>
       <c r="D399" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E399" t="n">
         <v>0</v>
@@ -9206,13 +9206,13 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>355</v>
+        <v>930</v>
       </c>
       <c r="C400" t="n">
-        <v>360</v>
+        <v>935</v>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E400" t="n">
         <v>0</v>
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>370</v>
+        <v>950</v>
       </c>
       <c r="C401" t="n">
-        <v>375</v>
+        <v>955</v>
       </c>
       <c r="D401" t="n">
         <v>1</v>
@@ -9250,13 +9250,13 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>380</v>
+        <v>1050</v>
       </c>
       <c r="C402" t="n">
-        <v>385</v>
+        <v>1055</v>
       </c>
       <c r="D402" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E402" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>395</v>
+        <v>1115</v>
       </c>
       <c r="C403" t="n">
-        <v>400</v>
+        <v>1120</v>
       </c>
       <c r="D403" t="n">
         <v>1</v>
@@ -9294,10 +9294,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>400</v>
+        <v>1150</v>
       </c>
       <c r="C404" t="n">
-        <v>405</v>
+        <v>1155</v>
       </c>
       <c r="D404" t="n">
         <v>1</v>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>415</v>
+        <v>1285</v>
       </c>
       <c r="C405" t="n">
-        <v>420</v>
+        <v>1290</v>
       </c>
       <c r="D405" t="n">
         <v>1</v>
@@ -9334,168 +9334,168 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>425</v>
+        <v>50</v>
       </c>
       <c r="C406" t="n">
-        <v>430</v>
+        <v>55</v>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E406" t="n">
         <v>0</v>
       </c>
       <c r="F406" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>435</v>
+        <v>60</v>
       </c>
       <c r="C407" t="n">
-        <v>440</v>
+        <v>65</v>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E407" t="n">
         <v>0</v>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="C408" t="n">
-        <v>465</v>
+        <v>75</v>
       </c>
       <c r="D408" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E408" t="n">
         <v>0</v>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="C409" t="n">
-        <v>475</v>
+        <v>85</v>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E409" t="n">
         <v>0</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>480</v>
+        <v>95</v>
       </c>
       <c r="C410" t="n">
-        <v>485</v>
+        <v>100</v>
       </c>
       <c r="D410" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E410" t="n">
         <v>0</v>
       </c>
       <c r="F410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>490</v>
+        <v>100</v>
       </c>
       <c r="C411" t="n">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E411" t="n">
         <v>0</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>510</v>
+        <v>115</v>
       </c>
       <c r="C412" t="n">
-        <v>515</v>
+        <v>120</v>
       </c>
       <c r="D412" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E412" t="n">
         <v>0</v>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>515</v>
+        <v>120</v>
       </c>
       <c r="C413" t="n">
-        <v>520</v>
+        <v>125</v>
       </c>
       <c r="D413" t="n">
         <v>1</v>
@@ -9504,42 +9504,42 @@
         <v>0</v>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>525</v>
+        <v>125</v>
       </c>
       <c r="C414" t="n">
-        <v>530</v>
+        <v>130</v>
       </c>
       <c r="D414" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E414" t="n">
         <v>0</v>
       </c>
       <c r="F414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>540</v>
+        <v>130</v>
       </c>
       <c r="C415" t="n">
-        <v>545</v>
+        <v>135</v>
       </c>
       <c r="D415" t="n">
         <v>1</v>
@@ -9548,42 +9548,42 @@
         <v>0</v>
       </c>
       <c r="F415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>555</v>
+        <v>135</v>
       </c>
       <c r="C416" t="n">
-        <v>560</v>
+        <v>140</v>
       </c>
       <c r="D416" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E416" t="n">
         <v>0</v>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>560</v>
+        <v>150</v>
       </c>
       <c r="C417" t="n">
-        <v>565</v>
+        <v>155</v>
       </c>
       <c r="D417" t="n">
         <v>1</v>
@@ -9592,64 +9592,64 @@
         <v>0</v>
       </c>
       <c r="F417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>570</v>
+        <v>155</v>
       </c>
       <c r="C418" t="n">
-        <v>575</v>
+        <v>160</v>
       </c>
       <c r="D418" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E418" t="n">
         <v>0</v>
       </c>
       <c r="F418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="C419" t="n">
-        <v>585</v>
+        <v>175</v>
       </c>
       <c r="D419" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E419" t="n">
         <v>0</v>
       </c>
       <c r="F419" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>585</v>
+        <v>175</v>
       </c>
       <c r="C420" t="n">
-        <v>590</v>
+        <v>180</v>
       </c>
       <c r="D420" t="n">
         <v>1</v>
@@ -9658,108 +9658,108 @@
         <v>0</v>
       </c>
       <c r="F420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>600</v>
+        <v>190</v>
       </c>
       <c r="C421" t="n">
-        <v>605</v>
+        <v>195</v>
       </c>
       <c r="D421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E421" t="n">
         <v>0</v>
       </c>
       <c r="F421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>625</v>
+        <v>200</v>
       </c>
       <c r="C422" t="n">
-        <v>630</v>
+        <v>205</v>
       </c>
       <c r="D422" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E422" t="n">
         <v>0</v>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>655</v>
+        <v>205</v>
       </c>
       <c r="C423" t="n">
-        <v>660</v>
+        <v>210</v>
       </c>
       <c r="D423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E423" t="n">
         <v>0</v>
       </c>
       <c r="F423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>695</v>
+        <v>215</v>
       </c>
       <c r="C424" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E424" t="n">
         <v>0</v>
       </c>
       <c r="F424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>835</v>
+        <v>225</v>
       </c>
       <c r="C425" t="n">
-        <v>840</v>
+        <v>230</v>
       </c>
       <c r="D425" t="n">
         <v>1</v>
@@ -9768,64 +9768,64 @@
         <v>0</v>
       </c>
       <c r="F425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>880</v>
+        <v>240</v>
       </c>
       <c r="C426" t="n">
-        <v>885</v>
+        <v>245</v>
       </c>
       <c r="D426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E426" t="n">
         <v>0</v>
       </c>
       <c r="F426" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>930</v>
+        <v>260</v>
       </c>
       <c r="C427" t="n">
-        <v>935</v>
+        <v>265</v>
       </c>
       <c r="D427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E427" t="n">
         <v>0</v>
       </c>
       <c r="F427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>950</v>
+        <v>290</v>
       </c>
       <c r="C428" t="n">
-        <v>955</v>
+        <v>295</v>
       </c>
       <c r="D428" t="n">
         <v>1</v>
@@ -9834,20 +9834,20 @@
         <v>0</v>
       </c>
       <c r="F428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>1050</v>
+        <v>310</v>
       </c>
       <c r="C429" t="n">
-        <v>1055</v>
+        <v>315</v>
       </c>
       <c r="D429" t="n">
         <v>1</v>
@@ -9856,20 +9856,20 @@
         <v>0</v>
       </c>
       <c r="F429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>1115</v>
+        <v>325</v>
       </c>
       <c r="C430" t="n">
-        <v>1120</v>
+        <v>330</v>
       </c>
       <c r="D430" t="n">
         <v>1</v>
@@ -9878,20 +9878,20 @@
         <v>0</v>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>1150</v>
+        <v>330</v>
       </c>
       <c r="C431" t="n">
-        <v>1155</v>
+        <v>335</v>
       </c>
       <c r="D431" t="n">
         <v>1</v>
@@ -9900,29 +9900,29 @@
         <v>0</v>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>W2W_sediment_fiber</t>
+          <t>W2W_ocean_all</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>1285</v>
+        <v>345</v>
       </c>
       <c r="C432" t="n">
-        <v>1290</v>
+        <v>350</v>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E432" t="n">
         <v>0</v>
       </c>
       <c r="F432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -9932,13 +9932,13 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="C433" t="n">
-        <v>55</v>
+        <v>445</v>
       </c>
       <c r="D433" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E433" t="n">
         <v>0</v>
@@ -9954,13 +9954,13 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>60</v>
+        <v>495</v>
       </c>
       <c r="C434" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="D434" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E434" t="n">
         <v>0</v>
@@ -9976,13 +9976,13 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>70</v>
+        <v>765</v>
       </c>
       <c r="C435" t="n">
-        <v>75</v>
+        <v>770</v>
       </c>
       <c r="D435" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E435" t="n">
         <v>0</v>
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>80</v>
+        <v>875</v>
       </c>
       <c r="C436" t="n">
-        <v>85</v>
+        <v>880</v>
       </c>
       <c r="D436" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E436" t="n">
         <v>0</v>
@@ -10016,17 +10016,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="C437" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="D437" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E437" t="n">
         <v>0</v>
@@ -10038,17 +10038,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C438" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="D438" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E438" t="n">
         <v>0</v>
@@ -10060,17 +10060,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="C439" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D439" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E439" t="n">
         <v>0</v>
@@ -10082,17 +10082,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C440" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E440" t="n">
         <v>0</v>
@@ -10104,17 +10104,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="C441" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="D441" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E441" t="n">
         <v>0</v>
@@ -10126,17 +10126,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C442" t="n">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E442" t="n">
         <v>0</v>
@@ -10148,17 +10148,17 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C443" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D443" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E443" t="n">
         <v>0</v>
@@ -10170,14 +10170,14 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C444" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D444" t="n">
         <v>1</v>
@@ -10192,17 +10192,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C445" t="n">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D445" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E445" t="n">
         <v>0</v>
@@ -10214,17 +10214,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C446" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D446" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E446" t="n">
         <v>0</v>
@@ -10236,17 +10236,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="C447" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="D447" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E447" t="n">
         <v>0</v>
@@ -10258,14 +10258,14 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C448" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="D448" t="n">
         <v>1</v>
@@ -10280,17 +10280,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="C449" t="n">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="D449" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E449" t="n">
         <v>0</v>
@@ -10302,17 +10302,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="C450" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E450" t="n">
         <v>0</v>
@@ -10324,17 +10324,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="C451" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E451" t="n">
         <v>0</v>
@@ -10346,14 +10346,14 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C452" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="D452" t="n">
         <v>2</v>
@@ -10368,14 +10368,14 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="C453" t="n">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="D453" t="n">
         <v>1</v>
@@ -10390,17 +10390,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="C454" t="n">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="D454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E454" t="n">
         <v>0</v>
@@ -10412,17 +10412,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="C455" t="n">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E455" t="n">
         <v>0</v>
@@ -10434,14 +10434,14 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>290</v>
+        <v>225</v>
       </c>
       <c r="C456" t="n">
-        <v>295</v>
+        <v>230</v>
       </c>
       <c r="D456" t="n">
         <v>1</v>
@@ -10456,17 +10456,17 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="C457" t="n">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="D457" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E457" t="n">
         <v>0</v>
@@ -10478,14 +10478,14 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="C458" t="n">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="D458" t="n">
         <v>1</v>
@@ -10500,7 +10500,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -10522,7 +10522,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -10544,7 +10544,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fragment</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -10566,36 +10566,36 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>495</v>
+        <v>75</v>
       </c>
       <c r="C462" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E462" t="n">
         <v>0</v>
       </c>
       <c r="F462" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>765</v>
+        <v>100</v>
       </c>
       <c r="C463" t="n">
-        <v>770</v>
+        <v>105</v>
       </c>
       <c r="D463" t="n">
         <v>1</v>
@@ -10604,20 +10604,20 @@
         <v>0</v>
       </c>
       <c r="F463" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>W2W_ocean_all</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>875</v>
+        <v>260</v>
       </c>
       <c r="C464" t="n">
-        <v>880</v>
+        <v>265</v>
       </c>
       <c r="D464" t="n">
         <v>1</v>
@@ -10626,754 +10626,116 @@
         <v>0</v>
       </c>
       <c r="F464" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>W2W_ocean_fragment</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>50</v>
+        <v>310</v>
       </c>
       <c r="C465" t="n">
-        <v>55</v>
+        <v>315</v>
       </c>
       <c r="D465" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E465" t="n">
         <v>0</v>
       </c>
       <c r="F465" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>W2W_ocean_fragment</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>60</v>
+        <v>325</v>
       </c>
       <c r="C466" t="n">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="D466" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E466" t="n">
         <v>0</v>
       </c>
       <c r="F466" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>W2W_ocean_fragment</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>70</v>
+        <v>495</v>
       </c>
       <c r="C467" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="D467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E467" t="n">
         <v>0</v>
       </c>
       <c r="F467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>W2W_ocean_fragment</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>80</v>
+        <v>765</v>
       </c>
       <c r="C468" t="n">
-        <v>85</v>
+        <v>770</v>
       </c>
       <c r="D468" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E468" t="n">
         <v>0</v>
       </c>
       <c r="F468" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>W2W_ocean_fragment</t>
+          <t>W2W_ocean_fiber</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>95</v>
+        <v>875</v>
       </c>
       <c r="C469" t="n">
-        <v>100</v>
+        <v>880</v>
       </c>
       <c r="D469" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E469" t="n">
         <v>0</v>
       </c>
       <c r="F469" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B470" t="n">
-        <v>100</v>
-      </c>
-      <c r="C470" t="n">
-        <v>105</v>
-      </c>
-      <c r="D470" t="n">
-        <v>12</v>
-      </c>
-      <c r="E470" t="n">
-        <v>0</v>
-      </c>
-      <c r="F470" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B471" t="n">
-        <v>115</v>
-      </c>
-      <c r="C471" t="n">
-        <v>120</v>
-      </c>
-      <c r="D471" t="n">
-        <v>9</v>
-      </c>
-      <c r="E471" t="n">
-        <v>0</v>
-      </c>
-      <c r="F471" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B472" t="n">
-        <v>120</v>
-      </c>
-      <c r="C472" t="n">
-        <v>125</v>
-      </c>
-      <c r="D472" t="n">
-        <v>1</v>
-      </c>
-      <c r="E472" t="n">
-        <v>0</v>
-      </c>
-      <c r="F472" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B473" t="n">
-        <v>125</v>
-      </c>
-      <c r="C473" t="n">
-        <v>130</v>
-      </c>
-      <c r="D473" t="n">
-        <v>5</v>
-      </c>
-      <c r="E473" t="n">
-        <v>0</v>
-      </c>
-      <c r="F473" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B474" t="n">
-        <v>130</v>
-      </c>
-      <c r="C474" t="n">
-        <v>135</v>
-      </c>
-      <c r="D474" t="n">
-        <v>2</v>
-      </c>
-      <c r="E474" t="n">
-        <v>0</v>
-      </c>
-      <c r="F474" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B475" t="n">
-        <v>135</v>
-      </c>
-      <c r="C475" t="n">
-        <v>140</v>
-      </c>
-      <c r="D475" t="n">
-        <v>5</v>
-      </c>
-      <c r="E475" t="n">
-        <v>0</v>
-      </c>
-      <c r="F475" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B476" t="n">
-        <v>145</v>
-      </c>
-      <c r="C476" t="n">
-        <v>150</v>
-      </c>
-      <c r="D476" t="n">
-        <v>1</v>
-      </c>
-      <c r="E476" t="n">
-        <v>0</v>
-      </c>
-      <c r="F476" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B477" t="n">
-        <v>150</v>
-      </c>
-      <c r="C477" t="n">
-        <v>155</v>
-      </c>
-      <c r="D477" t="n">
-        <v>1</v>
-      </c>
-      <c r="E477" t="n">
-        <v>0</v>
-      </c>
-      <c r="F477" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B478" t="n">
-        <v>155</v>
-      </c>
-      <c r="C478" t="n">
-        <v>160</v>
-      </c>
-      <c r="D478" t="n">
-        <v>4</v>
-      </c>
-      <c r="E478" t="n">
-        <v>0</v>
-      </c>
-      <c r="F478" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B479" t="n">
-        <v>170</v>
-      </c>
-      <c r="C479" t="n">
-        <v>175</v>
-      </c>
-      <c r="D479" t="n">
-        <v>3</v>
-      </c>
-      <c r="E479" t="n">
-        <v>0</v>
-      </c>
-      <c r="F479" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B480" t="n">
-        <v>175</v>
-      </c>
-      <c r="C480" t="n">
-        <v>180</v>
-      </c>
-      <c r="D480" t="n">
-        <v>1</v>
-      </c>
-      <c r="E480" t="n">
-        <v>0</v>
-      </c>
-      <c r="F480" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B481" t="n">
-        <v>190</v>
-      </c>
-      <c r="C481" t="n">
-        <v>195</v>
-      </c>
-      <c r="D481" t="n">
-        <v>2</v>
-      </c>
-      <c r="E481" t="n">
-        <v>0</v>
-      </c>
-      <c r="F481" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B482" t="n">
-        <v>200</v>
-      </c>
-      <c r="C482" t="n">
-        <v>205</v>
-      </c>
-      <c r="D482" t="n">
-        <v>1</v>
-      </c>
-      <c r="E482" t="n">
-        <v>0</v>
-      </c>
-      <c r="F482" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B483" t="n">
-        <v>205</v>
-      </c>
-      <c r="C483" t="n">
-        <v>210</v>
-      </c>
-      <c r="D483" t="n">
-        <v>2</v>
-      </c>
-      <c r="E483" t="n">
-        <v>0</v>
-      </c>
-      <c r="F483" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B484" t="n">
-        <v>215</v>
-      </c>
-      <c r="C484" t="n">
-        <v>220</v>
-      </c>
-      <c r="D484" t="n">
-        <v>2</v>
-      </c>
-      <c r="E484" t="n">
-        <v>0</v>
-      </c>
-      <c r="F484" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B485" t="n">
-        <v>225</v>
-      </c>
-      <c r="C485" t="n">
-        <v>230</v>
-      </c>
-      <c r="D485" t="n">
-        <v>1</v>
-      </c>
-      <c r="E485" t="n">
-        <v>0</v>
-      </c>
-      <c r="F485" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B486" t="n">
-        <v>240</v>
-      </c>
-      <c r="C486" t="n">
-        <v>245</v>
-      </c>
-      <c r="D486" t="n">
-        <v>3</v>
-      </c>
-      <c r="E486" t="n">
-        <v>0</v>
-      </c>
-      <c r="F486" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B487" t="n">
-        <v>290</v>
-      </c>
-      <c r="C487" t="n">
-        <v>295</v>
-      </c>
-      <c r="D487" t="n">
-        <v>1</v>
-      </c>
-      <c r="E487" t="n">
-        <v>0</v>
-      </c>
-      <c r="F487" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B488" t="n">
-        <v>330</v>
-      </c>
-      <c r="C488" t="n">
-        <v>335</v>
-      </c>
-      <c r="D488" t="n">
-        <v>1</v>
-      </c>
-      <c r="E488" t="n">
-        <v>0</v>
-      </c>
-      <c r="F488" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B489" t="n">
-        <v>345</v>
-      </c>
-      <c r="C489" t="n">
-        <v>350</v>
-      </c>
-      <c r="D489" t="n">
-        <v>2</v>
-      </c>
-      <c r="E489" t="n">
-        <v>0</v>
-      </c>
-      <c r="F489" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fragment</t>
-        </is>
-      </c>
-      <c r="B490" t="n">
-        <v>440</v>
-      </c>
-      <c r="C490" t="n">
-        <v>445</v>
-      </c>
-      <c r="D490" t="n">
-        <v>1</v>
-      </c>
-      <c r="E490" t="n">
-        <v>0</v>
-      </c>
-      <c r="F490" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B491" t="n">
-        <v>75</v>
-      </c>
-      <c r="C491" t="n">
-        <v>80</v>
-      </c>
-      <c r="D491" t="n">
-        <v>4</v>
-      </c>
-      <c r="E491" t="n">
-        <v>0</v>
-      </c>
-      <c r="F491" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B492" t="n">
-        <v>100</v>
-      </c>
-      <c r="C492" t="n">
-        <v>105</v>
-      </c>
-      <c r="D492" t="n">
-        <v>1</v>
-      </c>
-      <c r="E492" t="n">
-        <v>0</v>
-      </c>
-      <c r="F492" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B493" t="n">
-        <v>260</v>
-      </c>
-      <c r="C493" t="n">
-        <v>265</v>
-      </c>
-      <c r="D493" t="n">
-        <v>1</v>
-      </c>
-      <c r="E493" t="n">
-        <v>0</v>
-      </c>
-      <c r="F493" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B494" t="n">
-        <v>310</v>
-      </c>
-      <c r="C494" t="n">
-        <v>315</v>
-      </c>
-      <c r="D494" t="n">
-        <v>1</v>
-      </c>
-      <c r="E494" t="n">
-        <v>0</v>
-      </c>
-      <c r="F494" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B495" t="n">
-        <v>325</v>
-      </c>
-      <c r="C495" t="n">
-        <v>330</v>
-      </c>
-      <c r="D495" t="n">
-        <v>1</v>
-      </c>
-      <c r="E495" t="n">
-        <v>0</v>
-      </c>
-      <c r="F495" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B496" t="n">
-        <v>495</v>
-      </c>
-      <c r="C496" t="n">
-        <v>500</v>
-      </c>
-      <c r="D496" t="n">
-        <v>1</v>
-      </c>
-      <c r="E496" t="n">
-        <v>0</v>
-      </c>
-      <c r="F496" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B497" t="n">
-        <v>765</v>
-      </c>
-      <c r="C497" t="n">
-        <v>770</v>
-      </c>
-      <c r="D497" t="n">
-        <v>1</v>
-      </c>
-      <c r="E497" t="n">
-        <v>0</v>
-      </c>
-      <c r="F497" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>W2W_ocean_fiber</t>
-        </is>
-      </c>
-      <c r="B498" t="n">
-        <v>875</v>
-      </c>
-      <c r="C498" t="n">
-        <v>880</v>
-      </c>
-      <c r="D498" t="n">
-        <v>1</v>
-      </c>
-      <c r="E498" t="n">
-        <v>0</v>
-      </c>
-      <c r="F498" t="n">
         <v>1</v>
       </c>
     </row>
